--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,7 +431,7 @@
     <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
   </si>
   <si>
     <t>Practitioner.meta.versionId</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10362" uniqueCount="922">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2301,7 +2301,7 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:code}
 </t>
   </si>
   <si>
@@ -2364,7 +2364,10 @@
     <t>Coded representation of the qualification.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
+    <t>Specific qualification the practitioner has to provide a service.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
   </si>
   <si>
     <t>Diplome.codeDiplome</t>
@@ -2575,6 +2578,10 @@
     <t>Practitioner.qualification.code.coding</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>closed</t>
   </si>
   <si>
@@ -2588,6 +2595,9 @@
   </si>
   <si>
     <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.code.text</t>
@@ -2685,10 +2695,6 @@
     <t>Practitioner.qualification:exercicePro.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
   </si>
   <si>
@@ -2752,7 +2758,7 @@
     <t>savoirFaire</t>
   </si>
   <si>
-    <t>savoirFaire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.id</t>
@@ -25536,11 +25542,13 @@
         <v>83</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y170" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="Z170" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>83</v>
@@ -25582,7 +25590,7 @@
         <v>83</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>83</v>
@@ -25597,7 +25605,7 @@
         <v>737</v>
       </c>
       <c r="AS170" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AT170" t="s" s="2">
         <v>83</v>
@@ -25605,10 +25613,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25634,14 +25642,14 @@
         <v>263</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>83</v>
@@ -25690,7 +25698,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>84</v>
@@ -25726,10 +25734,10 @@
         <v>83</v>
       </c>
       <c r="AR171" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AS171" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AT171" t="s" s="2">
         <v>83</v>
@@ -25737,10 +25745,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -25766,10 +25774,10 @@
         <v>495</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -25820,7 +25828,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>84</v>
@@ -25856,7 +25864,7 @@
         <v>83</v>
       </c>
       <c r="AR172" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AS172" t="s" s="2">
         <v>83</v>
@@ -25867,13 +25875,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>731</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>83</v>
@@ -25898,7 +25906,7 @@
         <v>732</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>734</v>
@@ -25976,7 +25984,7 @@
         <v>83</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -25999,7 +26007,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>739</v>
@@ -26129,7 +26137,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>740</v>
@@ -26257,13 +26265,13 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>740</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>83</v>
@@ -26285,13 +26293,13 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -26389,10 +26397,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -26519,10 +26527,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -26651,13 +26659,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="B179" t="s" s="2">
-        <v>782</v>
-      </c>
       <c r="C179" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>83</v>
@@ -26760,7 +26768,7 @@
         <v>83</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -26783,10 +26791,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -26913,10 +26921,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -27043,10 +27051,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -27086,7 +27094,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>83</v>
@@ -27175,10 +27183,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -27238,7 +27246,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>83</v>
@@ -27303,13 +27311,13 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D184" t="s" s="2">
         <v>83</v>
@@ -27412,7 +27420,7 @@
         <v>83</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>83</v>
@@ -27435,10 +27443,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -27565,10 +27573,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -27695,10 +27703,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -27738,7 +27746,7 @@
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>83</v>
@@ -27827,10 +27835,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27890,7 +27898,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>83</v>
@@ -27955,13 +27963,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>83</v>
@@ -28064,7 +28072,7 @@
         <v>83</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>83</v>
@@ -28087,10 +28095,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -28217,10 +28225,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -28347,10 +28355,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -28390,7 +28398,7 @@
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="S192" t="s" s="2">
         <v>83</v>
@@ -28479,10 +28487,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -28542,7 +28550,7 @@
       </c>
       <c r="Y193" s="2"/>
       <c r="Z193" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>83</v>
@@ -28607,10 +28615,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -28650,7 +28658,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>83</v>
@@ -28739,10 +28747,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -28869,7 +28877,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>741</v>
@@ -29003,7 +29011,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>746</v>
@@ -29135,7 +29143,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>752</v>
@@ -29194,11 +29202,13 @@
         <v>83</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y198" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y198" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="Z198" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>83</v>
@@ -29255,7 +29265,7 @@
         <v>737</v>
       </c>
       <c r="AS198" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AT198" t="s" s="2">
         <v>83</v>
@@ -29263,10 +29273,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -29393,10 +29403,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -29487,7 +29497,7 @@
         <v>85</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>129</v>
@@ -29514,7 +29524,7 @@
         <v>83</v>
       </c>
       <c r="AR200" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS200" t="s" s="2">
         <v>83</v>
@@ -29525,10 +29535,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -29600,14 +29610,14 @@
         <v>83</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>735</v>
+        <v>826</v>
       </c>
       <c r="AC201" s="2"/>
       <c r="AD201" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AF201" t="s" s="2">
         <v>417</v>
@@ -29619,7 +29629,7 @@
         <v>85</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>112</v>
@@ -29657,13 +29667,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>83</v>
@@ -29726,7 +29736,7 @@
       </c>
       <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>83</v>
@@ -29753,7 +29763,7 @@
         <v>85</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>112</v>
@@ -29791,13 +29801,13 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>83</v>
@@ -29860,7 +29870,7 @@
       </c>
       <c r="Y203" s="2"/>
       <c r="Z203" t="s" s="2">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>83</v>
@@ -29887,7 +29897,7 @@
         <v>85</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ203" t="s" s="2">
         <v>112</v>
@@ -29925,10 +29935,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -30021,7 +30031,7 @@
         <v>100</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>112</v>
@@ -30059,10 +30069,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -30088,14 +30098,14 @@
         <v>263</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>83</v>
@@ -30144,7 +30154,7 @@
         <v>83</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>84</v>
@@ -30180,10 +30190,10 @@
         <v>83</v>
       </c>
       <c r="AR205" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AS205" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AT205" t="s" s="2">
         <v>83</v>
@@ -30191,10 +30201,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -30321,10 +30331,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -30453,10 +30463,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -30482,7 +30492,7 @@
         <v>270</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="M208" t="s" s="2">
         <v>272</v>
@@ -30562,7 +30572,7 @@
         <v>83</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>83</v>
@@ -30585,10 +30595,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -30614,7 +30624,7 @@
         <v>270</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>282</v>
@@ -30696,7 +30706,7 @@
         <v>83</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>83</v>
@@ -30719,10 +30729,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -30745,13 +30755,13 @@
         <v>83</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -30802,7 +30812,7 @@
         <v>83</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>84</v>
@@ -30826,7 +30836,7 @@
         <v>83</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>83</v>
@@ -30838,7 +30848,7 @@
         <v>83</v>
       </c>
       <c r="AR210" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AS210" t="s" s="2">
         <v>83</v>
@@ -30849,13 +30859,13 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>731</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>83</v>
@@ -30880,7 +30890,7 @@
         <v>732</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="M211" t="s" s="2">
         <v>734</v>
@@ -30981,7 +30991,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>739</v>
@@ -31111,7 +31121,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>740</v>
@@ -31243,7 +31253,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>741</v>
@@ -31377,7 +31387,7 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>746</v>
@@ -31509,7 +31519,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>752</v>
@@ -31568,11 +31578,13 @@
         <v>83</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y216" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y216" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="Z216" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>83</v>
@@ -31629,7 +31641,7 @@
         <v>737</v>
       </c>
       <c r="AS216" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AT216" t="s" s="2">
         <v>83</v>
@@ -31637,10 +31649,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -31767,10 +31779,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -31861,7 +31873,7 @@
         <v>85</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ218" t="s" s="2">
         <v>129</v>
@@ -31888,7 +31900,7 @@
         <v>83</v>
       </c>
       <c r="AR218" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS218" t="s" s="2">
         <v>83</v>
@@ -31899,10 +31911,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -31974,14 +31986,14 @@
         <v>83</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>861</v>
+        <v>826</v>
       </c>
       <c r="AC219" s="2"/>
       <c r="AD219" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE219" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AF219" t="s" s="2">
         <v>417</v>
@@ -31993,7 +32005,7 @@
         <v>85</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ219" t="s" s="2">
         <v>112</v>
@@ -32031,13 +32043,13 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D220" t="s" s="2">
         <v>83</v>
@@ -32062,7 +32074,7 @@
         <v>163</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="M220" t="s" s="2">
         <v>414</v>
@@ -32100,7 +32112,7 @@
       </c>
       <c r="Y220" s="2"/>
       <c r="Z220" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>83</v>
@@ -32127,7 +32139,7 @@
         <v>85</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ220" t="s" s="2">
         <v>112</v>
@@ -32136,7 +32148,7 @@
         <v>83</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>83</v>
@@ -32165,10 +32177,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C221" t="s" s="2">
         <v>355</v>
@@ -32196,7 +32208,7 @@
         <v>163</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="M221" t="s" s="2">
         <v>414</v>
@@ -32261,7 +32273,7 @@
         <v>85</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>112</v>
@@ -32270,7 +32282,7 @@
         <v>83</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>83</v>
@@ -32299,10 +32311,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -32395,7 +32407,7 @@
         <v>100</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>112</v>
@@ -32433,10 +32445,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -32462,14 +32474,14 @@
         <v>263</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -32518,7 +32530,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>84</v>
@@ -32554,10 +32566,10 @@
         <v>83</v>
       </c>
       <c r="AR223" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AS223" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AT223" t="s" s="2">
         <v>83</v>
@@ -32565,10 +32577,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -32695,10 +32707,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -32827,10 +32839,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -32856,7 +32868,7 @@
         <v>270</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="M226" t="s" s="2">
         <v>272</v>
@@ -32930,7 +32942,7 @@
         <v>83</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>83</v>
@@ -32959,10 +32971,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -32988,7 +33000,7 @@
         <v>270</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="M227" t="s" s="2">
         <v>282</v>
@@ -33064,7 +33076,7 @@
         <v>83</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>83</v>
@@ -33093,10 +33105,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -33122,10 +33134,10 @@
         <v>495</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -33176,7 +33188,7 @@
         <v>83</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>84</v>
@@ -33212,7 +33224,7 @@
         <v>83</v>
       </c>
       <c r="AR228" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AS228" t="s" s="2">
         <v>83</v>
@@ -33223,13 +33235,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>731</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>83</v>
@@ -33254,7 +33266,7 @@
         <v>732</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="M229" t="s" s="2">
         <v>734</v>
@@ -33355,7 +33367,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>739</v>
@@ -33485,7 +33497,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>740</v>
@@ -33617,7 +33629,7 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>741</v>
@@ -33751,7 +33763,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>746</v>
@@ -33883,7 +33895,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>752</v>
@@ -33942,11 +33954,13 @@
         <v>83</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y234" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="Z234" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>83</v>
@@ -33979,7 +33993,7 @@
         <v>112</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>83</v>
@@ -34003,7 +34017,7 @@
         <v>737</v>
       </c>
       <c r="AS234" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AT234" t="s" s="2">
         <v>83</v>
@@ -34011,10 +34025,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -34141,10 +34155,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -34235,7 +34249,7 @@
         <v>85</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>129</v>
@@ -34262,7 +34276,7 @@
         <v>83</v>
       </c>
       <c r="AR236" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS236" t="s" s="2">
         <v>83</v>
@@ -34273,10 +34287,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -34348,7 +34362,7 @@
         <v>83</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>861</v>
+        <v>826</v>
       </c>
       <c r="AC237" s="2"/>
       <c r="AD237" t="s" s="2">
@@ -34367,7 +34381,7 @@
         <v>85</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>112</v>
@@ -34405,13 +34419,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>83</v>
@@ -34436,7 +34450,7 @@
         <v>163</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="M238" t="s" s="2">
         <v>414</v>
@@ -34474,7 +34488,7 @@
       </c>
       <c r="Y238" s="2"/>
       <c r="Z238" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>83</v>
@@ -34501,7 +34515,7 @@
         <v>85</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>112</v>
@@ -34539,13 +34553,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>83</v>
@@ -34570,7 +34584,7 @@
         <v>163</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="M239" t="s" s="2">
         <v>414</v>
@@ -34608,7 +34622,7 @@
       </c>
       <c r="Y239" s="2"/>
       <c r="Z239" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>83</v>
@@ -34635,7 +34649,7 @@
         <v>85</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>112</v>
@@ -34673,10 +34687,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -34769,7 +34783,7 @@
         <v>100</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>112</v>
@@ -34807,10 +34821,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -34836,14 +34850,14 @@
         <v>263</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>83</v>
@@ -34892,7 +34906,7 @@
         <v>83</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>84</v>
@@ -34928,10 +34942,10 @@
         <v>83</v>
       </c>
       <c r="AR241" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AS241" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AT241" t="s" s="2">
         <v>83</v>
@@ -34939,10 +34953,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -35069,10 +35083,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -35201,10 +35215,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -35230,7 +35244,7 @@
         <v>270</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="M244" t="s" s="2">
         <v>272</v>
@@ -35301,7 +35315,7 @@
         <v>112</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>83</v>
@@ -35333,10 +35347,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -35362,7 +35376,7 @@
         <v>270</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="M245" t="s" s="2">
         <v>282</v>
@@ -35435,7 +35449,7 @@
         <v>112</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>83</v>
@@ -35467,10 +35481,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -35496,10 +35510,10 @@
         <v>495</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
@@ -35550,7 +35564,7 @@
         <v>83</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>84</v>
@@ -35586,7 +35600,7 @@
         <v>83</v>
       </c>
       <c r="AR246" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AS246" t="s" s="2">
         <v>83</v>
@@ -35597,10 +35611,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -35623,19 +35637,19 @@
         <v>83</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>83</v>
@@ -35664,7 +35678,7 @@
       </c>
       <c r="Y247" s="2"/>
       <c r="Z247" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>83</v>
@@ -35682,7 +35696,7 @@
         <v>83</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>84</v>
@@ -35715,10 +35729,10 @@
         <v>83</v>
       </c>
       <c r="AQ247" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="AR247" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="AS247" t="s" s="2">
         <v>83</v>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -24844,7 +24844,7 @@
         <v>85</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>83</v>
@@ -25894,7 +25894,7 @@
         <v>85</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>83</v>
